--- a/excel/templates/Pixel_Distributor_Admin.xlsx
+++ b/excel/templates/Pixel_Distributor_Admin.xlsx
@@ -5,20 +5,10 @@
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
     <sheet name="DEALER_MASTER" sheetId="2" r:id="rId2"/>
-    <sheet name="USER_ACCOUNTS" sheetId="3" r:id="rId3"/>
-    <sheet name="PERMISSIONS" sheetId="4" r:id="rId4"/>
-    <sheet name="PRODUCT_MASTER" sheetId="5" r:id="rId5"/>
-    <sheet name="INVENTORY" sheetId="6" r:id="rId6"/>
-    <sheet name="STOCK_IN" sheetId="7" r:id="rId7"/>
-    <sheet name="STOCK_OUT" sheetId="8" r:id="rId8"/>
-    <sheet name="STOCK_TRANSFER" sheetId="9" r:id="rId9"/>
-    <sheet name="ORDERS" sheetId="10" r:id="rId10"/>
-    <sheet name="CUSTOMERS" sheetId="11" r:id="rId11"/>
-    <sheet name="PAYMENTS" sheetId="12" r:id="rId12"/>
-    <sheet name="REPORTS" sheetId="13" r:id="rId13"/>
-    <sheet name="APP_CONFIG" sheetId="14" r:id="rId14"/>
-    <sheet name="ACTIVITY_LOG" sheetId="15" r:id="rId15"/>
-    <sheet name="SETTINGS" sheetId="16" r:id="rId16"/>
+    <sheet name="PRODUCT_MASTER" sheetId="3" r:id="rId3"/>
+    <sheet name="INVENTORY" sheetId="4" r:id="rId4"/>
+    <sheet name="ORDERS" sheetId="5" r:id="rId5"/>
+    <sheet name="ACTIVITY_LOG" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -427,31 +417,31 @@
         <v>Total Active Dealers</v>
       </c>
       <c r="B2">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Total Warehouse Valuation (INR)</v>
+        <v>Total Catalog SKUs</v>
       </c>
       <c r="B3">
-        <v>12500000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Outstanding Receivables (INR)</v>
+        <v>Total Orders Captured</v>
       </c>
       <c r="B4">
-        <v>3400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Orders Pending Dispatch</v>
-      </c>
-      <c r="B5">
-        <v>14</v>
+        <v>Last Sync Pull Timestamp</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-09-24T16:20:23.112Z</v>
       </c>
     </row>
   </sheetData>
@@ -461,226 +451,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Order_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Dealer_ID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Customer_Name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Grand_Total</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Payment_Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ORD-2026-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-09-24</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Apex Walkin</v>
-      </c>
-      <c r="E2">
-        <v>112000</v>
-      </c>
-      <c r="F2" t="str">
-        <v>COMPLETED</v>
-      </c>
-      <c r="G2" t="str">
-        <v>PAID</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Customer_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Dealer_ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Customer_Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="E1" t="str">
-        <v>City</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Total_Orders</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Total_Spent</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>CUST-101</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Rohan Mehta</v>
-      </c>
-      <c r="D2" t="str">
-        <v>+919833445566</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Mumbai</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>184000</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Payment_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Dealer_ID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Mode</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Reference_Number</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PAY-401</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-09-24</v>
-      </c>
-      <c r="C2" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="D2">
-        <v>112000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>UPI</v>
-      </c>
-      <c r="F2" t="str">
-        <v>UPI/260924/8819</v>
-      </c>
-      <c r="G2" t="str">
-        <v>VERIFIED</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Report_Type</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Metric_Period</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Monthly Sales by Dealer</v>
-      </c>
-      <c r="B2" t="str">
-        <v>September 2026</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:O4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Dealer_ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Price_Visibility</v>
+        <v>Business_Name</v>
       </c>
       <c r="C1" t="str">
-        <v>MRP_Visible</v>
+        <v>Owner_Name</v>
       </c>
       <c r="D1" t="str">
-        <v>Cost_Visible</v>
+        <v>Mobile</v>
       </c>
       <c r="E1" t="str">
-        <v>Can_Create_Orders</v>
+        <v>Email</v>
       </c>
       <c r="F1" t="str">
-        <v>Can_Request_Stock</v>
+        <v>Address</v>
+      </c>
+      <c r="G1" t="str">
+        <v>City</v>
+      </c>
+      <c r="H1" t="str">
+        <v>State</v>
+      </c>
+      <c r="I1" t="str">
+        <v>PIN</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Dealer_Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Price_Group</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Credit_Limit</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Assigned_Warehouse</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Outstanding_Bal</v>
       </c>
     </row>
     <row r="2">
@@ -688,167 +507,7 @@
         <v>DLR-1001</v>
       </c>
       <c r="B2" t="str">
-        <v>DEALER_AND_MRP</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Timestamp</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Actor</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Action</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Entity</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Entity_ID</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-09-24T10:00:00Z</v>
-      </c>
-      <c r="B2" t="str">
-        <v>admin@pixeldistributor.com</v>
-      </c>
-      <c r="C2" t="str">
-        <v>SYSTEM_INITIALIZED</v>
-      </c>
-      <c r="D2" t="str">
-        <v>SYSTEM</v>
-      </c>
-      <c r="E2" t="str">
-        <v>SYS-01</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Setting_Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Setting_Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>STANDARD_TAX_RATE</v>
-      </c>
-      <c r="B2" t="str">
-        <v>18%</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>STANDARD_CREDIT_TERMS_DAYS</v>
-      </c>
-      <c r="B3" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>MINIMUM_APP_VERSION</v>
-      </c>
-      <c r="B4" t="str">
-        <v>1.0.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Dealer_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Business_Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Owner_Name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Mobile</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Address</v>
-      </c>
-      <c r="G1" t="str">
-        <v>City</v>
-      </c>
-      <c r="H1" t="str">
-        <v>State</v>
-      </c>
-      <c r="I1" t="str">
-        <v>PIN</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Dealer_Type</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Price_Group</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Credit_Limit</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Assigned_Warehouse</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Apex Telecom &amp; Digital Store</v>
+        <v>Apex Telecom &amp; Digital (Dealer A)</v>
       </c>
       <c r="C2" t="str">
         <v>Rajesh Kumar</v>
@@ -857,7 +516,7 @@
         <v>+919876543210</v>
       </c>
       <c r="E2" t="str">
-        <v>rajesh@apextelecom.in</v>
+        <v>dealerA@apex.in</v>
       </c>
       <c r="F2" t="str">
         <v>42 Ring Road, Commercial Zone</v>
@@ -882,6 +541,12 @@
       </c>
       <c r="M2" t="str">
         <v>WH-MUMBAI-01</v>
+      </c>
+      <c r="N2" t="str">
+        <v>ACTIVE</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -889,7 +554,7 @@
         <v>DLR-1002</v>
       </c>
       <c r="B3" t="str">
-        <v>Supreme Mobiles &amp; Gadgets</v>
+        <v>Supreme Mobiles (Dealer B)</v>
       </c>
       <c r="C3" t="str">
         <v>Suresh Patel</v>
@@ -898,10 +563,10 @@
         <v>+919811223344</v>
       </c>
       <c r="E3" t="str">
-        <v>suresh@suprememobiles.in</v>
+        <v>dealerB@supreme.in</v>
       </c>
       <c r="F3" t="str">
-        <v>88 Station Road, Sector 4</v>
+        <v>88 Station Road</v>
       </c>
       <c r="G3" t="str">
         <v>Ahmedabad</v>
@@ -922,7 +587,13 @@
         <v>1000000</v>
       </c>
       <c r="M3" t="str">
-        <v>WH-AHM-01</v>
+        <v>WH-MUMBAI-01</v>
+      </c>
+      <c r="N3" t="str">
+        <v>ACTIVE</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -930,7 +601,7 @@
         <v>DLR-1003</v>
       </c>
       <c r="B4" t="str">
-        <v>City Connect Retail Hub</v>
+        <v>City Connect Retail (Dealer C)</v>
       </c>
       <c r="C4" t="str">
         <v>Anil Deshmukh</v>
@@ -939,10 +610,10 @@
         <v>+919922334455</v>
       </c>
       <c r="E4" t="str">
-        <v>anil@cityconnect.in</v>
+        <v>dealerC@cityconnect.in</v>
       </c>
       <c r="F4" t="str">
-        <v>15 Gandhi Square, Market Area</v>
+        <v>15 Gandhi Square</v>
       </c>
       <c r="G4" t="str">
         <v>Pune</v>
@@ -965,185 +636,22 @@
       <c r="M4" t="str">
         <v>WH-MUMBAI-01</v>
       </c>
+      <c r="N4" t="str">
+        <v>ACTIVE</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>User_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Dealer_ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Display_Name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Role</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>usr_admin_01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>CENTRAL</v>
-      </c>
-      <c r="C2" t="str">
-        <v>admin@pixeldistributor.com</v>
-      </c>
-      <c r="D2" t="str">
-        <v>System Administrator</v>
-      </c>
-      <c r="E2" t="str">
-        <v>+919800000001</v>
-      </c>
-      <c r="F2" t="str">
-        <v>SUPER_ADMIN</v>
-      </c>
-      <c r="G2" t="str">
-        <v>ACTIVE</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>usr_dlr_1001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="C3" t="str">
-        <v>rajesh@apextelecom.in</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Rajesh Kumar</v>
-      </c>
-      <c r="E3" t="str">
-        <v>+919876543210</v>
-      </c>
-      <c r="F3" t="str">
-        <v>DEALER</v>
-      </c>
-      <c r="G3" t="str">
-        <v>ACTIVE</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Dealer_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>User_ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Dashboard</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Inventory</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Orders</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Customers</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Payments</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Reports</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>usr_dlr_1001</v>
-      </c>
-      <c r="C2" t="str">
-        <v>VIEW</v>
-      </c>
-      <c r="D2" t="str">
-        <v>EDIT</v>
-      </c>
-      <c r="E2" t="str">
-        <v>EDIT</v>
-      </c>
-      <c r="F2" t="str">
-        <v>VIEW</v>
-      </c>
-      <c r="G2" t="str">
-        <v>VIEW</v>
-      </c>
-      <c r="H2" t="str">
-        <v>VIEW</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>DLR-1002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>usr_dlr_1002</v>
-      </c>
-      <c r="C3" t="str">
-        <v>VIEW</v>
-      </c>
-      <c r="D3" t="str">
-        <v>VIEW</v>
-      </c>
-      <c r="E3" t="str">
-        <v>CREATE</v>
-      </c>
-      <c r="F3" t="str">
-        <v>HIDDEN</v>
-      </c>
-      <c r="G3" t="str">
-        <v>HIDDEN</v>
-      </c>
-      <c r="H3" t="str">
-        <v>HIDDEN</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
   <sheetData>
     <row r="1">
@@ -1189,7 +697,7 @@
         <v>Pixel Ultra 256GB Titanium</v>
       </c>
       <c r="C2" t="str">
-        <v>Smartphones</v>
+        <v>Smartphones &amp; Tablets</v>
       </c>
       <c r="D2" t="str">
         <v>Pixel</v>
@@ -1224,7 +732,7 @@
         <v>Pixel Pro 128GB Obsidian</v>
       </c>
       <c r="C3" t="str">
-        <v>Smartphones</v>
+        <v>Smartphones &amp; Tablets</v>
       </c>
       <c r="D3" t="str">
         <v>Pixel</v>
@@ -1293,270 +801,202 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Warehouse_ID</v>
+        <v>Inventory_ID</v>
       </c>
       <c r="B1" t="str">
+        <v>Location_Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Location_ID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Dealer_ID</v>
+      </c>
+      <c r="E1" t="str">
         <v>SKU</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
         <v>Product_Name</v>
       </c>
-      <c r="D1" t="str">
-        <v>Opening_Quantity</v>
-      </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Reserved_Qty</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Available_Qty</v>
+      </c>
+      <c r="J1" t="str">
         <v>Reorder_Level</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Unit_Cost</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>CENTRAL_WAREHOUSE_WH-MUMBAI-01_PX-ULTRA-256</v>
+      </c>
+      <c r="B2" t="str">
+        <v>CENTRAL_WAREHOUSE</v>
+      </c>
+      <c r="C2" t="str">
         <v>WH-MUMBAI-01</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
+        <v>CENTRAL</v>
+      </c>
+      <c r="E2" t="str">
         <v>PX-ULTRA-256</v>
       </c>
-      <c r="C2" t="str">
+      <c r="F2" t="str">
         <v>Pixel Ultra 256GB Titanium</v>
       </c>
-      <c r="D2">
-        <v>150</v>
-      </c>
-      <c r="E2">
+      <c r="G2">
+        <v>250</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>250</v>
+      </c>
+      <c r="J2">
         <v>20</v>
-      </c>
-      <c r="F2">
-        <v>52000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>CENTRAL_WAREHOUSE_WH-MUMBAI-01_PX-PRO-128</v>
+      </c>
+      <c r="B3" t="str">
+        <v>CENTRAL_WAREHOUSE</v>
+      </c>
+      <c r="C3" t="str">
         <v>WH-MUMBAI-01</v>
       </c>
-      <c r="B3" t="str">
+      <c r="D3" t="str">
+        <v>CENTRAL</v>
+      </c>
+      <c r="E3" t="str">
         <v>PX-PRO-128</v>
       </c>
-      <c r="C3" t="str">
+      <c r="F3" t="str">
         <v>Pixel Pro 128GB Obsidian</v>
       </c>
-      <c r="D3">
-        <v>200</v>
-      </c>
-      <c r="E3">
-        <v>25</v>
-      </c>
-      <c r="F3">
-        <v>41000</v>
+      <c r="G3">
+        <v>180</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>180</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>CENTRAL_WAREHOUSE_WH-MUMBAI-01_PX-BUDS-PRO</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CENTRAL_WAREHOUSE</v>
+      </c>
+      <c r="C4" t="str">
         <v>WH-MUMBAI-01</v>
       </c>
-      <c r="B4" t="str">
+      <c r="D4" t="str">
+        <v>CENTRAL</v>
+      </c>
+      <c r="E4" t="str">
         <v>PX-BUDS-PRO</v>
       </c>
-      <c r="C4" t="str">
+      <c r="F4" t="str">
         <v>Pixel Buds Pro Wireless ANC</v>
       </c>
-      <c r="D4">
-        <v>500</v>
-      </c>
-      <c r="E4">
+      <c r="G4">
+        <v>400</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>400</v>
+      </c>
+      <c r="J4">
         <v>50</v>
-      </c>
-      <c r="F4">
-        <v>8500</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Entry_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Warehouse_ID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>SKU</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Vendor</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Invoice_Ref</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>INW-8001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-09-20</v>
-      </c>
-      <c r="C2" t="str">
-        <v>WH-MUMBAI-01</v>
-      </c>
-      <c r="D2" t="str">
-        <v>PX-ULTRA-256</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Pixel Global Mfg</v>
-      </c>
-      <c r="G2" t="str">
-        <v>INV-GL-991</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Exit_ID</v>
+        <v>Timestamp</v>
       </c>
       <c r="B1" t="str">
-        <v>Date</v>
+        <v>Actor</v>
       </c>
       <c r="C1" t="str">
-        <v>Warehouse_ID</v>
+        <v>Action</v>
       </c>
       <c r="D1" t="str">
-        <v>SKU</v>
+        <v>Entity</v>
       </c>
       <c r="E1" t="str">
-        <v>Quantity</v>
+        <v>Entity_ID</v>
       </c>
       <c r="F1" t="str">
-        <v>Reason</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Approved_By</v>
+        <v>Dealer_Scope</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>OUT-9001</v>
+        <v>2026-09-24T16:20:23.108Z</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-22</v>
+        <v>admin@pixeldistributor.com</v>
       </c>
       <c r="C2" t="str">
-        <v>WH-MUMBAI-01</v>
+        <v>EXCEL_SYNC_PUSH_EXECUTED</v>
       </c>
       <c r="D2" t="str">
-        <v>PX-BUDS-PRO</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+        <v>workbook</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Pixel_Distributor_Admin.xlsx</v>
       </c>
       <c r="F2" t="str">
-        <v>DAMAGED</v>
-      </c>
-      <c r="G2" t="str">
-        <v>usr_inv_mgr</v>
+        <v>CENTRAL</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Transfer_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Source_Warehouse</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Destination_Dealer</v>
-      </c>
-      <c r="E1" t="str">
-        <v>SKU</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Quantity</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Tracking_Ref</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>TRF-501</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-09-23</v>
-      </c>
-      <c r="C2" t="str">
-        <v>WH-MUMBAI-01</v>
-      </c>
-      <c r="D2" t="str">
-        <v>DLR-1001</v>
-      </c>
-      <c r="E2" t="str">
-        <v>PX-ULTRA-256</v>
-      </c>
-      <c r="F2">
-        <v>25</v>
-      </c>
-      <c r="G2" t="str">
-        <v>DELIVERED</v>
-      </c>
-      <c r="H2" t="str">
-        <v>BLUEDART-88210</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/excel/templates/Pixel_Distributor_Admin.xlsx
+++ b/excel/templates/Pixel_Distributor_Admin.xlsx
@@ -441,7 +441,7 @@
         <v>Last Sync Pull Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-24T16:20:23.112Z</v>
+        <v>2026-09-24T16:32:32.131Z</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-24T16:20:23.108Z</v>
+        <v>2026-09-24T16:32:32.125Z</v>
       </c>
       <c r="B2" t="str">
         <v>admin@pixeldistributor.com</v>

--- a/excel/templates/Pixel_Distributor_Admin.xlsx
+++ b/excel/templates/Pixel_Distributor_Admin.xlsx
@@ -441,7 +441,7 @@
         <v>Last Sync Pull Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-24T16:32:32.131Z</v>
+        <v>2026-09-24T16:56:51.826Z</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-24T16:32:32.125Z</v>
+        <v>2026-09-24T16:56:51.821Z</v>
       </c>
       <c r="B2" t="str">
         <v>admin@pixeldistributor.com</v>

--- a/excel/templates/Pixel_Distributor_Admin.xlsx
+++ b/excel/templates/Pixel_Distributor_Admin.xlsx
@@ -441,7 +441,7 @@
         <v>Last Sync Pull Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-24T16:56:51.826Z</v>
+        <v>2026-09-24T17:26:44.141Z</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +976,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-24T16:56:51.821Z</v>
+        <v>2026-09-24T17:26:44.124Z</v>
       </c>
       <c r="B2" t="str">
         <v>admin@pixeldistributor.com</v>

--- a/excel/templates/Pixel_Distributor_Admin.xlsx
+++ b/excel/templates/Pixel_Distributor_Admin.xlsx
@@ -6,8 +6,8 @@
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
     <sheet name="DEALER_MASTER" sheetId="2" r:id="rId2"/>
     <sheet name="PRODUCT_MASTER" sheetId="3" r:id="rId3"/>
-    <sheet name="INVENTORY" sheetId="4" r:id="rId4"/>
-    <sheet name="ORDERS" sheetId="5" r:id="rId5"/>
+    <sheet name="INVENTORY_BALANCES" sheetId="4" r:id="rId4"/>
+    <sheet name="PURCHASE_ORDERS" sheetId="5" r:id="rId5"/>
     <sheet name="ACTIVITY_LOG" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,39 +414,55 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Total Active Dealers</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
+        <v>Platform Mode</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Plan A: Excel-First Administration</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Total Catalog SKUs</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
+        <v>Cloud Database</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Google Cloud Firestore (pixel-distributor)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Total Orders Captured</v>
+        <v>Total Active Dealers</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Total Catalog SKUs</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Total Orders Captured</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>Last Sync Pull Timestamp</v>
       </c>
-      <c r="B5" t="str">
-        <v>2026-09-24T17:26:44.141Z</v>
+      <c r="B7" t="str">
+        <v>2026-09-24T18:07:42.222Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -976,10 +992,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-24T17:26:44.124Z</v>
+        <v>2026-09-24T18:07:42.210Z</v>
       </c>
       <c r="B2" t="str">
-        <v>admin@pixeldistributor.com</v>
+        <v>naren7703@gmail.com</v>
       </c>
       <c r="C2" t="str">
         <v>EXCEL_SYNC_PUSH_EXECUTED</v>
